--- a/artfynd/A 34590-2021 artfynd.xlsx
+++ b/artfynd/A 34590-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34590-2021 artfynd.xlsx
+++ b/artfynd/A 34590-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>82464300</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554811.2748661096</v>
+        <v>554811</v>
       </c>
       <c r="R2" t="n">
-        <v>6769477.975143978</v>
+        <v>6769478</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -749,19 +744,9 @@
           <t>1986-07-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1986-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,12 +785,7 @@
         <v>82464299</v>
       </c>
       <c r="B3" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554811.2748661096</v>
+        <v>554811</v>
       </c>
       <c r="R3" t="n">
-        <v>6769477.975143978</v>
+        <v>6769478</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -875,19 +855,9 @@
           <t>1986-07-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1986-07-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,12 +896,7 @@
         <v>82464250</v>
       </c>
       <c r="B4" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104028</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554811.2748661096</v>
+        <v>554811</v>
       </c>
       <c r="R4" t="n">
-        <v>6769477.975143978</v>
+        <v>6769478</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1001,19 +966,9 @@
           <t>1986-07-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1986-07-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 34590-2021 artfynd.xlsx
+++ b/artfynd/A 34590-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82464300</v>
       </c>
       <c r="B2" t="n">
-        <v>98499</v>
+        <v>98505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>82464299</v>
       </c>
       <c r="B3" t="n">
-        <v>98581</v>
+        <v>98587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>82464250</v>
       </c>
       <c r="B4" t="n">
-        <v>104028</v>
+        <v>104036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34590-2021 artfynd.xlsx
+++ b/artfynd/A 34590-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82464300</v>
       </c>
       <c r="B2" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>82464299</v>
       </c>
       <c r="B3" t="n">
-        <v>98587</v>
+        <v>98590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>82464250</v>
       </c>
       <c r="B4" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34590-2021 artfynd.xlsx
+++ b/artfynd/A 34590-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82464300</v>
       </c>
       <c r="B2" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>82464299</v>
       </c>
       <c r="B3" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>82464250</v>
       </c>
       <c r="B4" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
